--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484101_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484101_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.579800000000001</v>
+        <v>9.3246</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3203</v>
+        <v>6.7284</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2595</v>
+        <v>2.5962</v>
       </c>
       <c r="G2" t="n">
         <v>5.8306</v>
@@ -610,13 +610,13 @@
         <v>2.7774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6314</v>
+        <v>0.1133</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4989</v>
+        <v>0.907</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1303</v>
+        <v>-0.7937</v>
       </c>
       <c r="V2" t="n">
         <v>0.6032</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7937</v>
+        <v>3.4034</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3655</v>
+        <v>1.0594</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4282</v>
+        <v>2.344</v>
       </c>
       <c r="G3" t="n">
         <v>4.0175</v>
@@ -688,13 +688,13 @@
         <v>1.1903</v>
       </c>
       <c r="S3" t="n">
-        <v>0.641</v>
+        <v>0.2508</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1224</v>
+        <v>0.8163</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4813</v>
+        <v>-0.5655</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0713</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. SEVILLANO PUIG</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3138</v>
+        <v>1.6574</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8052</v>
+        <v>0.2995</v>
       </c>
       <c r="F4" t="n">
-        <v>3.119</v>
+        <v>1.358</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5659</v>
+        <v>1.7424</v>
       </c>
       <c r="H4" t="n">
-        <v>2.096</v>
+        <v>0.5894</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5301</v>
+        <v>1.1531</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9794</v>
+        <v>2.0508</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6585</v>
+        <v>0.6452</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.6379</v>
+        <v>1.4057</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5452</v>
+        <v>-0.3084</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4374</v>
+        <v>-0.0558</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1078</v>
+        <v>-0.2526</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3806</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.1661</v>
+        <v>-1.9838</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9816</v>
+        <v>0.5101</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6018</v>
+        <v>0.2325</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6202</v>
+        <v>0.2777</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1469</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.7384</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4085</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>G. SEVILLANO PUIG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5554</v>
+        <v>1.0436</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1974</v>
+        <v>-2.1315</v>
       </c>
       <c r="F5" t="n">
-        <v>1.358</v>
+        <v>3.1751</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7424</v>
+        <v>0.5659</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5894</v>
+        <v>2.096</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1531</v>
+        <v>-1.5301</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0508</v>
+        <v>-0.9794</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6452</v>
+        <v>1.6585</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4057</v>
+        <v>-2.6379</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3084</v>
+        <v>1.5452</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0558</v>
+        <v>0.4374</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2526</v>
+        <v>1.1078</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5952</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9838</v>
+        <v>-4.1661</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4081</v>
+        <v>0.7113</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1304</v>
+        <v>1.2755</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2777</v>
+        <v>-0.5641</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>2.1469</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.7384</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.4085</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8475</v>
+        <v>-0.3977</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8531</v>
+        <v>-2.1487</v>
       </c>
       <c r="F6" t="n">
-        <v>2.0055</v>
+        <v>1.751</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.308</v>
+        <v>0.1001</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.6283</v>
+        <v>-0.3935</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3202</v>
+        <v>0.4935</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.275</v>
+        <v>-0.6994</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.0381</v>
+        <v>0.0509</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7631</v>
+        <v>-0.7503</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.033</v>
+        <v>0.7995</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-0.4444</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5572</v>
+        <v>1.2439</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1903</v>
+        <v>-4.1661</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5281</v>
+        <v>0.8828</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6122</v>
+        <v>0.907</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9157999999999999</v>
+        <v>-0.0242</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.266</v>
+        <v>0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.266</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9121</v>
+        <v>-0.6722</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.176</v>
+        <v>-1.0491</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2639</v>
+        <v>0.3768</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.661</v>
+        <v>-1.7364</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2874</v>
+        <v>-1.2545</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9483</v>
+        <v>-0.4819</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0653</v>
+        <v>-1.1002</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0552</v>
+        <v>-0.4627</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>-0.6375</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6363</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3425</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0688</v>
+        <v>0.1555</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S7" t="n">
-        <v>0.344</v>
+        <v>0.8658</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2494</v>
+        <v>1.043</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5934</v>
+        <v>-0.1772</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1144</v>
+        <v>-1.1187</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5569</v>
+        <v>-1.074</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4424</v>
+        <v>-0.0447</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1001</v>
+        <v>-0.661</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3935</v>
+        <v>0.2874</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4935</v>
+        <v>-0.9483</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6994</v>
+        <v>0.0653</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0509</v>
+        <v>-0.0552</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7503</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7995</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4444</v>
+        <v>0.3425</v>
       </c>
       <c r="O8" t="n">
-        <v>1.2439</v>
+        <v>-1.0688</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.9838</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1661</v>
+        <v>-0.9919</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1822</v>
+        <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1661</v>
+        <v>0.1374</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4989</v>
+        <v>-0.1474</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3328</v>
+        <v>0.2848</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1747</v>
+        <v>-1.6066</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3551</v>
+        <v>-3.4211</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1805</v>
+        <v>1.8145</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7364</v>
+        <v>-3.2837</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2545</v>
+        <v>-1.6382</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4819</v>
+        <v>-1.6455</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1002</v>
+        <v>-3.3932</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4627</v>
+        <v>-2.0003</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6375</v>
+        <v>-1.3929</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6363</v>
+        <v>0.1095</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.3621</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1555</v>
+        <v>-0.2526</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-3.1741</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3634</v>
+        <v>-0.1488</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7369</v>
+        <v>-0.1359</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3736</v>
+        <v>-0.0129</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>3.0162</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.2821</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7724</v>
+        <v>-1.6586</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7272</v>
+        <v>-3.1591</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9548</v>
+        <v>1.5005</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2837</v>
+        <v>-2.308</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6382</v>
+        <v>-3.6283</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6455</v>
+        <v>1.3202</v>
       </c>
       <c r="J10" t="n">
-        <v>-3.3932</v>
+        <v>-2.275</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0003</v>
+        <v>-3.0381</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3929</v>
+        <v>0.7631</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1095</v>
+        <v>-0.033</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3621</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2526</v>
+        <v>0.5572</v>
       </c>
       <c r="P10" t="n">
+        <v>0.1984</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-1.1903</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-3.1741</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3146</v>
+        <v>0.717</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.442</v>
+        <v>0.3062</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1274</v>
+        <v>0.4108</v>
       </c>
       <c r="V10" t="n">
-        <v>3.0162</v>
+        <v>-0.266</v>
       </c>
       <c r="W10" t="n">
-        <v>3.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-0.266</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0611</v>
+        <v>-2.6148</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5386</v>
+        <v>-4.2325</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4774</v>
+        <v>1.6177</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8907</v>
@@ -1312,13 +1312,13 @@
         <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5672</v>
+        <v>-1.1209</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7481</v>
+        <v>-0.4421</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8191000000000001</v>
+        <v>-0.6788</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,31 +1345,31 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.3605</v>
+        <v>7.360400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.1289</v>
+        <v>-9.1287</v>
       </c>
       <c r="F12" t="n">
-        <v>16.4892</v>
+        <v>16.4891</v>
       </c>
       <c r="G12" t="n">
         <v>2.376699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9592000000000009</v>
+        <v>-0.9592000000000007</v>
       </c>
       <c r="I12" t="n">
-        <v>3.3359</v>
+        <v>3.335900000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4148</v>
+        <v>-1.414800000000001</v>
       </c>
       <c r="K12" t="n">
         <v>-3.195399999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.780599999999999</v>
+        <v>1.7806</v>
       </c>
       <c r="M12" t="n">
         <v>3.7914</v>
@@ -1390,13 +1390,13 @@
         <v>15.8708</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9191</v>
+        <v>2.9188</v>
       </c>
       <c r="T12" t="n">
-        <v>4.762</v>
+        <v>4.7621</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.843</v>
+        <v>-1.8431</v>
       </c>
       <c r="V12" t="n">
         <v>6.0322</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2889</v>
+        <v>4.8715</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9995000000000001</v>
+        <v>1.2035</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2894</v>
+        <v>3.668</v>
       </c>
       <c r="G13" t="n">
         <v>2.7681</v>
@@ -1468,13 +1468,13 @@
         <v>3.1741</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5208</v>
+        <v>0.1034</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1869</v>
+        <v>0.0172</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7077</v>
+        <v>0.0863</v>
       </c>
       <c r="V13" t="n">
         <v>1.2065</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3917</v>
+        <v>2.0557</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5394</v>
+        <v>0.0728</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9311</v>
+        <v>1.983</v>
       </c>
       <c r="G14" t="n">
         <v>2.0964</v>
@@ -1546,13 +1546,13 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4902</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1846</v>
+        <v>-0.5724</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3056</v>
+        <v>-0.2538</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6032</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.5592</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5782</v>
+        <v>0.6802</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0473</v>
+        <v>-0.121</v>
       </c>
       <c r="G15" t="n">
         <v>1.3831</v>
@@ -1624,13 +1624,13 @@
         <v>0.1984</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2505</v>
+        <v>0.1842</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1247</v>
+        <v>-0.0227</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3752</v>
+        <v>0.2069</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2065</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. ESONO MBA</t>
+          <t>A. BELTRAN MATA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7106</v>
+        <v>0.5026</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.236</v>
+        <v>2.0348</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4746</v>
+        <v>-1.5322</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.4774</v>
+        <v>1.2373</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6575</v>
+        <v>0.6505</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1801</v>
+        <v>0.5869</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9674</v>
+        <v>1.995</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.128</v>
+        <v>0.903</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1606</v>
+        <v>1.092</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.51</v>
+        <v>-0.7577</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5295</v>
+        <v>-0.2525</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0195</v>
+        <v>-0.5051</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7935</v>
+        <v>2.7774</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1822</v>
+        <v>-0.1984</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3887</v>
+        <v>2.9758</v>
       </c>
       <c r="S16" t="n">
-        <v>2.0922</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9136</v>
+        <v>0.2382</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8213</v>
+        <v>-1.0714</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.532</v>
+        <v>-2.6789</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.532</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BELTRAN MATA</t>
+          <t>L. MARTÍN LLAVERÍA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1944</v>
+        <v>-1.7628</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8105</v>
+        <v>-4.0972</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0049</v>
+        <v>2.3343</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2373</v>
+        <v>-0.999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6505</v>
+        <v>-0.8669</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5869</v>
+        <v>-0.1321</v>
       </c>
       <c r="J17" t="n">
-        <v>1.995</v>
+        <v>-1.779</v>
       </c>
       <c r="K17" t="n">
-        <v>0.903</v>
+        <v>-1.2193</v>
       </c>
       <c r="L17" t="n">
-        <v>1.092</v>
+        <v>-0.5597</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7577</v>
+        <v>0.7799</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2525</v>
+        <v>0.3523</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5051</v>
+        <v>0.4276</v>
       </c>
       <c r="P17" t="n">
-        <v>2.7774</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1984</v>
+        <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9758</v>
+        <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.5302</v>
+        <v>-0.5654</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9862</v>
+        <v>-0.136</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.5441</v>
+        <v>-0.4295</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.6789</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6789</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. MARTÍN LLAVERÍA</t>
+          <t>J. ESONO MBA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2908</v>
+        <v>-2.1467</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.7093</v>
+        <v>-1.8685</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4185</v>
+        <v>-0.2782</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.999</v>
+        <v>-1.4774</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8669</v>
+        <v>-1.6575</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1321</v>
+        <v>0.1801</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.779</v>
+        <v>-0.9674</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2193</v>
+        <v>-1.128</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5597</v>
+        <v>0.1606</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7799</v>
+        <v>-0.51</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3523</v>
+        <v>-0.5295</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4276</v>
+        <v>0.0195</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1984</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.1822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0934</v>
+        <v>0.6561</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7481</v>
+        <v>1.2811</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3453</v>
+        <v>-0.625</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4151</v>
+        <v>-2.1567</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.5917</v>
+        <v>-4.6937</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1765</v>
+        <v>2.537</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9379999999999999</v>
@@ -1936,13 +1936,13 @@
         <v>2.9758</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0803</v>
+        <v>-0.8219</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0511</v>
+        <v>-0.0509</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1315</v>
+        <v>-0.771</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8835</v>
+        <v>-4.016</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2655</v>
+        <v>-3.2858</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.618</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6905</v>
@@ -2014,13 +2014,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6087</v>
+        <v>0.4761</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1087</v>
+        <v>1.0884</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5</v>
+        <v>-0.6122</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.172</v>
+        <v>-4.587</v>
       </c>
       <c r="E21" t="n">
         <v>-6.2694</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0975</v>
+        <v>1.6824</v>
       </c>
       <c r="G21" t="n">
         <v>-3.7567</v>
@@ -2092,13 +2092,13 @@
         <v>2.9758</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.197</v>
+        <v>-0.6121</v>
       </c>
       <c r="T21" t="n">
         <v>0.0001</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1972</v>
+        <v>-0.6122</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0118</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.360299999999999</v>
+        <v>-6.6802</v>
       </c>
       <c r="E22" t="n">
-        <v>-16.2231</v>
+        <v>-16.2233</v>
       </c>
       <c r="F22" t="n">
-        <v>8.8628</v>
+        <v>9.542999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3767</v>
@@ -2161,7 +2161,7 @@
         <v>-1.7805</v>
       </c>
       <c r="P22" t="n">
-        <v>3.9676</v>
+        <v>3.967599999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-15.8706</v>
@@ -2170,13 +2170,13 @@
         <v>19.8385</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.918899999999999</v>
+        <v>-2.2389</v>
       </c>
       <c r="T22" t="n">
         <v>1.843</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.7621</v>
+        <v>-4.0819</v>
       </c>
       <c r="V22" t="n">
         <v>-6.0324</v>
